--- a/data/trans_dic/P33B_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R1-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,91; 28,66</t>
+          <t>20,86; 27,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,92; 39,56</t>
+          <t>35,07; 40,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 33,95</t>
+          <t>29,9; 33,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,52</t>
+          <t>9,51; 12,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 17,34</t>
+          <t>16,36; 19,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 13,88</t>
+          <t>13,15; 15,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,77</t>
+          <t>8,03; 12,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,19</t>
+          <t>11,72; 16,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 13,72</t>
+          <t>10,49; 13,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,55</t>
+          <t>11,74; 13,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 21,16</t>
+          <t>20,2; 22,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,09</t>
+          <t>16,39; 17,98</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>277481</t>
+          <t>309217</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406062</t>
+          <t>447047</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>112801; 147569</t>
+          <t>120674; 158464</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>255486; 297990</t>
+          <t>288043; 328623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>377577; 430482</t>
+          <t>418565; 474777</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>222433</t>
+          <t>238586</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>337750</t>
+          <t>382777</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560183</t>
+          <t>621364</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>158584; 263806</t>
+          <t>212093; 272385</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>240086; 388033</t>
+          <t>355255; 415756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>449083; 628391</t>
+          <t>578587; 668592</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>72931</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90239</t>
+          <t>101330</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155468</t>
+          <t>174261</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50868; 82569</t>
+          <t>57133; 90745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76851; 106916</t>
+          <t>86159; 118351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135246; 179317</t>
+          <t>151765; 198050</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>705470</t>
+          <t>793324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1121713</t>
+          <t>1242671</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>324201; 467710</t>
+          <t>413057; 491810</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>578078; 772427</t>
+          <t>752797; 838646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>977673; 1213800</t>
+          <t>1188012; 1303181</t>
         </is>
       </c>
     </row>
